--- a/teams/benefits-portfolio/benefits-intake-optimization/post-go-live/21p-601/21P-601 Post-Go-Live Submission Tracker.xlsx
+++ b/teams/benefits-portfolio/benefits-intake-optimization/post-go-live/21p-601/21P-601 Post-Go-Live Submission Tracker.xlsx
@@ -1,13 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f465efd6b01b8bba/Documents/GingerHorizonsGroup_Projects/AgileSix/BIO/GH/benefits-intake-optimization/teams/benefits-portfolio/benefits-intake-optimization/post-go-live/21p-601/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_C72C412D6D0B49B47531FC19036639BD795BB99D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EEF0022-1415-4809-B5A9-7DAD07D50F47}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="21P-601" sheetId="1" r:id="rId4"/>
+    <sheet name="21P-601" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="5lxnqwu+06XqmNBA4QGxkuZYA9q46Pmc5Z6q5IUZj3Y="/>
     </ext>
@@ -93,40 +113,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
-    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color rgb="FF0E2841"/>
       <name val="Play"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0E2841"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -136,15 +154,25 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF45B0E1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -159,48 +187,45 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="14" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -390,55 +415,54 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="40.13"/>
-    <col customWidth="1" min="2" max="2" width="17.25"/>
-    <col customWidth="1" min="3" max="3" width="21.38"/>
-    <col customWidth="1" min="4" max="4" width="11.13"/>
-    <col customWidth="1" min="5" max="5" width="15.25"/>
-    <col customWidth="1" min="6" max="6" width="9.25"/>
-    <col customWidth="1" min="7" max="26" width="8.63"/>
+    <col min="1" max="1" width="40.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" customWidth="1"/>
+    <col min="7" max="26" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="23.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>3790.0</v>
+        <v>3790</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <f>COUNTIF(A8:A100000,"&lt;&gt;")</f>
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C4" s="4">
         <f>B4/B3</f>
-        <v>0.002374670185</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>8.4432717678100261E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -447,7 +471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -467,294 +491,294 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="8">
-        <v>46066.0</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="C8" s="7">
+        <v>46066</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="6">
-        <v>6.8952723E7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="s">
+      <c r="F8" s="2">
+        <v>68952723</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="8">
-        <v>46059.0</v>
+      <c r="C9" s="7">
+        <v>46059</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="9">
-        <v>46062.0</v>
-      </c>
-      <c r="F9" s="6">
-        <v>6.8744347E7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
+      <c r="E9" s="8">
+        <v>46062</v>
+      </c>
+      <c r="F9" s="2">
+        <v>68744347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="8">
-        <v>46058.0</v>
+      <c r="C10" s="7">
+        <v>46058</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="9">
-        <v>46059.0</v>
-      </c>
-      <c r="F10" s="6">
-        <v>6.8701018E7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
+      <c r="E10" s="8">
+        <v>46059</v>
+      </c>
+      <c r="F10" s="2">
+        <v>68701018</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="8">
-        <v>46053.0</v>
+      <c r="C11" s="7">
+        <v>46053</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="9">
-        <v>46056.0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>6.8525211E7</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="E11" s="8">
+        <v>46056</v>
+      </c>
+      <c r="F11" s="2">
+        <v>68525211</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="10">
-        <v>46043.0</v>
+      <c r="C12" s="9">
+        <v>46043</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="10">
-        <v>46043.0</v>
+      <c r="E12" s="9">
+        <v>46043</v>
       </c>
       <c r="F12" s="2">
-        <v>6.8094025E7</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="s">
+        <v>68094025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="10">
-        <v>46043.0</v>
-      </c>
-      <c r="D13" s="11" t="s">
+      <c r="C13" s="9">
+        <v>46043</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="10">
-        <v>46043.0</v>
+      <c r="E13" s="9">
+        <v>46043</v>
       </c>
       <c r="F13" s="2">
-        <v>6.8093288E7</v>
-      </c>
-      <c r="G13" s="8"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="s">
+        <v>68093288</v>
+      </c>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="10">
-        <v>46038.0</v>
+      <c r="C14" s="9">
+        <v>46038</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="10">
-        <v>46038.0</v>
+      <c r="E14" s="9">
+        <v>46038</v>
       </c>
       <c r="F14" s="2">
-        <v>6.8041488E7</v>
-      </c>
-      <c r="G14" s="8"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="s">
+        <v>68041488</v>
+      </c>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="10">
-        <v>46037.0</v>
+      <c r="C15" s="9">
+        <v>46037</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="10">
-        <v>46037.0</v>
+      <c r="E15" s="9">
+        <v>46037</v>
       </c>
       <c r="F15" s="2">
-        <v>6.80012E7</v>
-      </c>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="s">
+        <v>68001200</v>
+      </c>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="10">
-        <v>46035.0</v>
+      <c r="C16" s="9">
+        <v>46035</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="10">
-        <v>46035.0</v>
+      <c r="E16" s="9">
+        <v>46035</v>
       </c>
       <c r="F16" s="2">
-        <v>6.7787787E7</v>
-      </c>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17">
-      <c r="C17" s="10"/>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18">
-      <c r="C18" s="10"/>
-      <c r="E18" s="10"/>
-    </row>
-    <row r="19">
-      <c r="C19" s="10"/>
-      <c r="E19" s="10"/>
-    </row>
-    <row r="20">
-      <c r="C20" s="10"/>
-      <c r="E20" s="10"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="C21" s="10"/>
-      <c r="E21" s="10"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="C22" s="10"/>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="C23" s="10"/>
-      <c r="E23" s="10"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="C24" s="10"/>
-      <c r="E24" s="10"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="C25" s="10"/>
-      <c r="E25" s="10"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="C26" s="10"/>
-      <c r="E26" s="10"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="C27" s="10"/>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="C28" s="10"/>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="C29" s="10"/>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="C30" s="10"/>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="C31" s="10"/>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="C32" s="10"/>
-      <c r="E32" s="10"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="C33" s="10"/>
-      <c r="E33" s="10"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="C34" s="10"/>
-      <c r="E34" s="10"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="C35" s="10"/>
-      <c r="E35" s="10"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="C36" s="10"/>
-      <c r="E36" s="10"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="C37" s="10"/>
-      <c r="E37" s="10"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="C38" s="10"/>
-      <c r="E38" s="10"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="C39" s="10"/>
-      <c r="E39" s="10"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="C40" s="10"/>
-      <c r="E40" s="10"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="C41" s="10"/>
-      <c r="E41" s="10"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+        <v>67787787</v>
+      </c>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="3:5">
+      <c r="C17" s="9"/>
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18" spans="3:5">
+      <c r="C18" s="9"/>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="3:5">
+      <c r="C19" s="9"/>
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" spans="3:5">
+      <c r="C20" s="9"/>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C21" s="9"/>
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C22" s="9"/>
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C23" s="9"/>
+      <c r="E23" s="9"/>
+    </row>
+    <row r="24" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C24" s="9"/>
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C25" s="9"/>
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C26" s="9"/>
+      <c r="E26" s="9"/>
+    </row>
+    <row r="27" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C27" s="9"/>
+      <c r="E27" s="9"/>
+    </row>
+    <row r="28" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C28" s="9"/>
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C29" s="9"/>
+      <c r="E29" s="9"/>
+    </row>
+    <row r="30" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C30" s="9"/>
+      <c r="E30" s="9"/>
+    </row>
+    <row r="31" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C31" s="9"/>
+      <c r="E31" s="9"/>
+    </row>
+    <row r="32" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C32" s="9"/>
+      <c r="E32" s="9"/>
+    </row>
+    <row r="33" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C33" s="9"/>
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C34" s="9"/>
+      <c r="E34" s="9"/>
+    </row>
+    <row r="35" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C35" s="9"/>
+      <c r="E35" s="9"/>
+    </row>
+    <row r="36" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C36" s="9"/>
+      <c r="E36" s="9"/>
+    </row>
+    <row r="37" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C37" s="9"/>
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C38" s="9"/>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C39" s="9"/>
+      <c r="E39" s="9"/>
+    </row>
+    <row r="40" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C40" s="9"/>
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41" spans="3:5" ht="15.75" customHeight="1">
+      <c r="C41" s="9"/>
+      <c r="E41" s="9"/>
+    </row>
+    <row r="42" spans="3:5" ht="15.75" customHeight="1"/>
+    <row r="43" spans="3:5" ht="15.75" customHeight="1"/>
+    <row r="44" spans="3:5" ht="15.75" customHeight="1"/>
+    <row r="45" spans="3:5" ht="15.75" customHeight="1"/>
+    <row r="46" spans="3:5" ht="15.75" customHeight="1"/>
+    <row r="47" spans="3:5" ht="15.75" customHeight="1"/>
+    <row r="48" spans="3:5" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1708,9 +1732,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>